--- a/backend/temp_an.xlsx
+++ b/backend/temp_an.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,156 +413,1218 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Student Name</t>
+          <t>student_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Missed Deadlines</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Hours Spent</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Days Since Access</t>
+          <t>phone_number</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>course_name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>logins</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>assignments</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>quizzes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>forum</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>study_hours</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>activities_completed</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>محمد علي</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Salma Jaziri</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>salma1@mail.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>050000001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H2" t="n">
+        <v>75</v>
+      </c>
+      <c r="I2" t="n">
+        <v>40</v>
+      </c>
+      <c r="J2" t="n">
+        <v>95</v>
+      </c>
+      <c r="K2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L2" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>فاطمة أحمد</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Karim Sassi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>karim2@mail.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>050000002</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>150</v>
+      </c>
+      <c r="G3" t="n">
+        <v>90</v>
+      </c>
+      <c r="H3" t="n">
+        <v>85</v>
+      </c>
+      <c r="I3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J3" t="n">
+        <v>97</v>
+      </c>
+      <c r="K3" t="n">
+        <v>25</v>
+      </c>
+      <c r="L3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Omar Ben Ali</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>omar3@mail.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>050000003</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J4" t="n">
+        <v>60</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Amine Trabelsi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>amine4@mail.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>050000004</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>55</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Leila Mansour</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>leila5@mail.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>050000005</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" t="n">
+        <v>75</v>
+      </c>
+      <c r="H6" t="n">
+        <v>70</v>
+      </c>
+      <c r="I6" t="n">
+        <v>35</v>
+      </c>
+      <c r="J6" t="n">
+        <v>90</v>
+      </c>
+      <c r="K6" t="n">
+        <v>18</v>
+      </c>
+      <c r="L6" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Youssef Kallel</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>youssef6@mail.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>050000006</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H7" t="n">
+        <v>45</v>
+      </c>
+      <c r="I7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J7" t="n">
+        <v>75</v>
+      </c>
+      <c r="K7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" t="n">
         <v>9</v>
       </c>
-      <c r="D3" t="n">
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hanen Gharbi</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>hanen7@mail.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>050000007</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>110</v>
+      </c>
+      <c r="G8" t="n">
+        <v>85</v>
+      </c>
+      <c r="H8" t="n">
+        <v>80</v>
+      </c>
+      <c r="I8" t="n">
+        <v>45</v>
+      </c>
+      <c r="J8" t="n">
+        <v>93</v>
+      </c>
+      <c r="K8" t="n">
+        <v>22</v>
+      </c>
+      <c r="L8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mohamed Riahi</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mohamed8@mail.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>050000008</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>20</v>
+      </c>
+      <c r="G9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>40</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Nour Ben Salem</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>nour9@mail.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>050000009</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>95</v>
+      </c>
+      <c r="G10" t="n">
+        <v>70</v>
+      </c>
+      <c r="H10" t="n">
+        <v>65</v>
+      </c>
+      <c r="I10" t="n">
+        <v>30</v>
+      </c>
+      <c r="J10" t="n">
+        <v>88</v>
+      </c>
+      <c r="K10" t="n">
+        <v>17</v>
+      </c>
+      <c r="L10" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sami Feki</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sami10@mail.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>050000010</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>50</v>
+      </c>
+      <c r="G11" t="n">
+        <v>40</v>
+      </c>
+      <c r="H11" t="n">
+        <v>35</v>
+      </c>
+      <c r="I11" t="n">
+        <v>15</v>
+      </c>
+      <c r="J11" t="n">
+        <v>70</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rim Toumi</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>rim11@mail.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>050000011</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>130</v>
+      </c>
+      <c r="G12" t="n">
+        <v>90</v>
+      </c>
+      <c r="H12" t="n">
+        <v>88</v>
+      </c>
+      <c r="I12" t="n">
+        <v>55</v>
+      </c>
+      <c r="J12" t="n">
+        <v>98</v>
+      </c>
+      <c r="K12" t="n">
+        <v>28</v>
+      </c>
+      <c r="L12" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ali Ben Amor</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ali12@mail.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>050000012</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G13" t="n">
+        <v>15</v>
+      </c>
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>50</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ines Khemiri</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ines13@mail.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>050000013</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>105</v>
+      </c>
+      <c r="G14" t="n">
+        <v>78</v>
+      </c>
+      <c r="H14" t="n">
+        <v>72</v>
+      </c>
+      <c r="I14" t="n">
+        <v>38</v>
+      </c>
+      <c r="J14" t="n">
+        <v>92</v>
+      </c>
+      <c r="K14" t="n">
+        <v>19</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Firas Hadded</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>firas14@mail.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>050000014</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>45</v>
+      </c>
+      <c r="G15" t="n">
+        <v>35</v>
+      </c>
+      <c r="H15" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" t="n">
+        <v>12</v>
+      </c>
+      <c r="J15" t="n">
+        <v>68</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sarah Ben Youssef</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>sarah15@mail.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>050000015</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>115</v>
+      </c>
+      <c r="G16" t="n">
+        <v>88</v>
+      </c>
+      <c r="H16" t="n">
+        <v>82</v>
+      </c>
+      <c r="I16" t="n">
+        <v>48</v>
+      </c>
+      <c r="J16" t="n">
+        <v>96</v>
+      </c>
+      <c r="K16" t="n">
+        <v>24</v>
+      </c>
+      <c r="L16" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Hichem Miled</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>hichem16@mail.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>050000016</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>35</v>
+      </c>
+      <c r="G17" t="n">
+        <v>25</v>
+      </c>
+      <c r="H17" t="n">
+        <v>20</v>
+      </c>
+      <c r="I17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>60</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Amel Rekik</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>amel17@mail.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>050000017</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>90</v>
+      </c>
+      <c r="G18" t="n">
+        <v>65</v>
+      </c>
+      <c r="H18" t="n">
+        <v>60</v>
+      </c>
+      <c r="I18" t="n">
+        <v>28</v>
+      </c>
+      <c r="J18" t="n">
+        <v>85</v>
+      </c>
+      <c r="K18" t="n">
+        <v>15</v>
+      </c>
+      <c r="L18" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Walid Guesmi</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>walid18@mail.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>050000018</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>70</v>
+      </c>
+      <c r="G19" t="n">
+        <v>55</v>
+      </c>
+      <c r="H19" t="n">
+        <v>50</v>
+      </c>
+      <c r="I19" t="n">
+        <v>22</v>
+      </c>
+      <c r="J19" t="n">
+        <v>78</v>
+      </c>
+      <c r="K19" t="n">
+        <v>12</v>
+      </c>
+      <c r="L19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Meriem Baccar</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>meriem19@mail.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>050000019</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>125</v>
+      </c>
+      <c r="G20" t="n">
+        <v>92</v>
+      </c>
+      <c r="H20" t="n">
+        <v>90</v>
+      </c>
+      <c r="I20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J20" t="n">
+        <v>99</v>
+      </c>
+      <c r="K20" t="n">
+        <v>30</v>
+      </c>
+      <c r="L20" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Lotfi Karray</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>lotfi20@mail.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>050000020</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>15</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>علي محمود</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" t="n">
+      <c r="J21" t="n">
+        <v>30</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ayoub Jlassi</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ayoub21@mail.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>050000021</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>85</v>
+      </c>
+      <c r="G22" t="n">
+        <v>60</v>
+      </c>
+      <c r="H22" t="n">
+        <v>55</v>
+      </c>
+      <c r="I22" t="n">
+        <v>25</v>
+      </c>
+      <c r="J22" t="n">
+        <v>82</v>
+      </c>
+      <c r="K22" t="n">
+        <v>14</v>
+      </c>
+      <c r="L22" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rania Ghannouchi</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>rania22@mail.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>050000022</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>95</v>
+      </c>
+      <c r="G23" t="n">
+        <v>72</v>
+      </c>
+      <c r="H23" t="n">
+        <v>68</v>
+      </c>
+      <c r="I23" t="n">
+        <v>33</v>
+      </c>
+      <c r="J23" t="n">
+        <v>89</v>
+      </c>
+      <c r="K23" t="n">
+        <v>16</v>
+      </c>
+      <c r="L23" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Adel Ben Said</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>adel23@mail.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>050000023</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>55</v>
+      </c>
+      <c r="G24" t="n">
+        <v>45</v>
+      </c>
+      <c r="H24" t="n">
+        <v>40</v>
+      </c>
+      <c r="I24" t="n">
+        <v>18</v>
+      </c>
+      <c r="J24" t="n">
+        <v>72</v>
+      </c>
+      <c r="K24" t="n">
+        <v>9</v>
+      </c>
+      <c r="L24" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Maha Dridi</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>maha24@mail.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>050000024</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>140</v>
+      </c>
+      <c r="G25" t="n">
+        <v>95</v>
+      </c>
+      <c r="H25" t="n">
+        <v>92</v>
+      </c>
+      <c r="I25" t="n">
+        <v>65</v>
+      </c>
+      <c r="J25" t="n">
+        <v>99</v>
+      </c>
+      <c r="K25" t="n">
+        <v>32</v>
+      </c>
+      <c r="L25" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Zied Boussetta</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>zied25@mail.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>050000025</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>نور السيد</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>هناء حسن</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>10</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="I26" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>خالد عمر</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>مريم صالح</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+      <c r="J26" t="n">
+        <v>25</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>أحمد جمال</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="L26" t="n">
         <v>1</v>
       </c>
     </row>
